--- a/to_rdf/basefile.xlsx
+++ b/to_rdf/basefile.xlsx
@@ -8,36 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shiho\Documents\Study\Unibo\LOD\aLODofTea\to_rdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E7D5777-594E-45AE-9C14-1226D269F50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC6FBF5-3FF6-48AE-A20C-E5AEE222FE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-100" windowWidth="21467" windowHeight="11443" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="21467" windowHeight="11443" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" r:id="rId1"/>
-    <sheet name="other" sheetId="2" r:id="rId2"/>
-    <sheet name="uri" sheetId="3" r:id="rId3"/>
-    <sheet name="rikyu-portrait" sheetId="4" r:id="rId4"/>
-    <sheet name="teabowl" sheetId="5" r:id="rId5"/>
-    <sheet name="teascoop" sheetId="6" r:id="rId6"/>
-    <sheet name="japanese-bridge" sheetId="7" r:id="rId7"/>
-    <sheet name="kimono" sheetId="8" r:id="rId8"/>
-    <sheet name="tea-ceremony-painting" sheetId="10" r:id="rId9"/>
-    <sheet name="samurai-woodblock" sheetId="9" r:id="rId10"/>
-    <sheet name="book-of-tea" sheetId="11" r:id="rId11"/>
-    <sheet name="teagarden" sheetId="12" r:id="rId12"/>
-    <sheet name="ikebana-book" sheetId="13" r:id="rId13"/>
+    <sheet name="Sheet1" sheetId="14" r:id="rId2"/>
+    <sheet name="other" sheetId="2" r:id="rId3"/>
+    <sheet name="uri" sheetId="3" r:id="rId4"/>
+    <sheet name="rikyu-portrait" sheetId="4" r:id="rId5"/>
+    <sheet name="teabowl" sheetId="5" r:id="rId6"/>
+    <sheet name="teascoop" sheetId="6" r:id="rId7"/>
+    <sheet name="japanese-bridge" sheetId="7" r:id="rId8"/>
+    <sheet name="kimono" sheetId="8" r:id="rId9"/>
+    <sheet name="tea-ceremony-painting" sheetId="10" r:id="rId10"/>
+    <sheet name="samurai-woodblock" sheetId="9" r:id="rId11"/>
+    <sheet name="book-of-tea" sheetId="11" r:id="rId12"/>
+    <sheet name="teagarden" sheetId="12" r:id="rId13"/>
+    <sheet name="ikebana-book" sheetId="13" r:id="rId14"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId14" roundtripDataChecksum="ALZr6qiTXSA0pk2//JLRGpBBaW7ZPUmF76Fj5fv5uE4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId15" roundtripDataChecksum="ALZr6qiTXSA0pk2//JLRGpBBaW7ZPUmF76Fj5fv5uE4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="310">
   <si>
     <t>rikyu-portrait</t>
   </si>
@@ -929,13 +930,133 @@
   </si>
   <si>
     <t>tea:person_okakura-kakuzo</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Institution</t>
+  </si>
+  <si>
+    <t>Book of Tea</t>
+  </si>
+  <si>
+    <t>Library of Congress</t>
+  </si>
+  <si>
+    <t>Portrait of Sen no Rikyu</t>
+  </si>
+  <si>
+    <t>The Tea Scoop of Rikyu</t>
+  </si>
+  <si>
+    <t>EDM
+(Europeana Data Model)</t>
+  </si>
+  <si>
+    <t>EDM</t>
+  </si>
+  <si>
+    <t>Woodblock Print of Samurai in Tea Ceremony</t>
+  </si>
+  <si>
+    <t>Tea Bowl</t>
+  </si>
+  <si>
+    <t>Item Type</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>Book</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>Painting</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>Ceramic</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>Costume</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>MODS
+DC
+MARCXML</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>CIDOC-CRM</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>BIBFRAME</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>Woodblock print</t>
+  </si>
+  <si>
+    <t>Bamboo</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>The Metropolitan Museum of Art</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>British Museum</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>Europeana</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>Internet Archive
+ARCHIVE</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>National Gallery of Art</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>MARCXML</t>
+  </si>
+  <si>
+    <t>Metadata Standard Provided by the Institution</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>Chosen Metadata Standard</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>Invitation to a Tea Ceremony</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>Illustrated Book</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>Ikebana Hinagata Densho</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>Mysterious Japan</t>
+    <phoneticPr fontId="7"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1021,8 +1142,25 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1089,8 +1227,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF356854"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1133,12 +1289,184 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF356854"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF356854"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF356854"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFF6F8F9"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFF6F8F9"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF356854"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1215,6 +1543,51 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4457,6 +4830,168 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB372515-F0FB-4041-9D02-F6D45CAAC945}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" customWidth="1"/>
+    <col min="3" max="3" width="56.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7"/>
+  <hyperlinks>
+    <hyperlink ref="C9" r:id="rId1" xr:uid="{EABEC07E-B774-46A3-9436-EB9F999B092F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC12B5D5-F0FF-4534-B3C9-AF24D3B7F2F0}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4585,7 +5120,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4C5BC5-6A3A-4D1A-B9A7-7D8EC839CC13}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4791,7 +5326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48BF80E6-3BCB-4F1A-B012-397C5C86C40D}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4908,7 +5443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576A44E4-398D-477E-BF46-E13CCA28B474}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5027,6 +5562,210 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABC080A-AFC5-46D3-9029-E3D3C621FB04}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="16.3984375" customWidth="1"/>
+    <col min="3" max="3" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.09765625" customWidth="1"/>
+    <col min="5" max="5" width="15.296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="40.450000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="40.450000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>293</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="27.15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="27.15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>297</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="40.450000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>306</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="40.450000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="28" t="s">
+        <v>286</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="27.15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="27.15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="27.15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="31" t="s">
+        <v>309</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="27.15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="27.15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>302</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>294</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C1004"/>
   <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="14.95" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -6689,7 +7428,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:B999"/>
   <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="14.95" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -9776,7 +10515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9BB55B7-5FA8-4CF7-8308-CD473F1DBC70}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9916,7 +10655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E702E3FA-9759-4307-92D2-ACDE9D3E34BB}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10067,7 +10806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B7BD4D6-EFD5-4DC5-AA23-95A4BCADFC44}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10196,7 +10935,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6D9FCB-E537-4ED8-80BE-6D0B2E829B99}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10347,7 +11086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3886F07-F635-44E6-B5DE-62EF06851B9F}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10474,166 +11213,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB372515-F0FB-4041-9D02-F6D45CAAC945}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="26.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" customWidth="1"/>
-    <col min="3" max="3" width="56.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="8">
-        <v>1881</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>273</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="7"/>
-  <hyperlinks>
-    <hyperlink ref="C9" r:id="rId1" xr:uid="{EABEC07E-B774-46A3-9436-EB9F999B092F}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>